--- a/docentes/Ángel Martínez Noe Cristobal - Estadisticos 20212.xlsx
+++ b/docentes/Ángel Martínez Noe Cristobal - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -74,6 +74,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>ANALI</t>
   </si>
 </sst>
 </file>
@@ -471,22 +480,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>34</v>
       </c>
       <c r="G2">
-        <v>91.89</v>
+        <v>94.44</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -497,22 +506,22 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>34</v>
       </c>
       <c r="G3">
-        <v>91.89</v>
+        <v>94.44</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -549,22 +558,22 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F5">
         <v>24</v>
       </c>
       <c r="G5">
-        <v>82.76000000000001</v>
+        <v>80</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -614,19 +623,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>94.44</v>
+      </c>
+      <c r="H2">
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -637,19 +649,22 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>94.44</v>
+      </c>
+      <c r="H3">
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -663,16 +678,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>96.97</v>
+      </c>
+      <c r="H4">
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -683,19 +701,22 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -745,22 +766,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>34</v>
       </c>
       <c r="G2">
-        <v>91.89</v>
+        <v>94.44</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -771,22 +792,22 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>34</v>
       </c>
       <c r="G3">
-        <v>91.89</v>
+        <v>94.44</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -803,16 +824,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>93.94</v>
+        <v>96.97</v>
       </c>
       <c r="H4">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -823,22 +844,22 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F5">
         <v>24</v>
       </c>
       <c r="G5">
-        <v>82.76000000000001</v>
+        <v>80</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -848,7 +869,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -878,6 +899,29 @@
         <v>18</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920191</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Ángel Martínez Noe Cristobal - Estadisticos 20212.xlsx
+++ b/docentes/Ángel Martínez Noe Cristobal - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -76,10 +76,28 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>DE LA TEJA</t>
+  </si>
+  <si>
     <t>ARIAS</t>
   </si>
   <si>
+    <t>OLIVERA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
+  </si>
+  <si>
+    <t>ALISSON FERNANDA</t>
   </si>
   <si>
     <t>ANALI</t>
@@ -869,7 +887,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -901,16 +919,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920191</v>
+        <v>20330051920204</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -919,6 +937,52 @@
         <v>12</v>
       </c>
       <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920218</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920191</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ángel Martínez Noe Cristobal - Estadisticos 20212.xlsx
+++ b/docentes/Ángel Martínez Noe Cristobal - Estadisticos 20212.xlsx
@@ -799,7 +799,7 @@
         <v>94.44</v>
       </c>
       <c r="H2">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -825,7 +825,7 @@
         <v>94.44</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -842,16 +842,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -877,7 +877,7 @@
         <v>80</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
